--- a/tools/seo/ads/merkcampagne/merkcampagne-overzicht.xlsx
+++ b/tools/seo/ads/merkcampagne/merkcampagne-overzicht.xlsx
@@ -418,116 +418,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Campagne</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Advertentiegroep</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max. bod (€)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Landingspagina</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Zoekwoorden (exact + woordgroep)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Kop 1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kop 2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kop 3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Kop 4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Kop 5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Kop 6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Kop 7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Kop 8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Kop 9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Kop 10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Kop 11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Kop 12</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Kop 13</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Kop 14</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Kop 15</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Beschrijving 1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Beschrijving 2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Beschrijving 3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Beschrijving 4</t>
         </is>
@@ -536,110 +546,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>The Hunt - Algemeen</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>escape game the hunt, the hunt escape game, escapegamethehunt, the hunt escape room, the hunt city game, the hunt outdoor escape</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>The Hunt Escape Game</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Outdoor Escape Game</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest The Hunt</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Bedrijfsuitje The Hunt</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in jouw stad. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -648,110 +668,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>The Hunt Groningen</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-groningen/</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>the hunt groningen, escape game the hunt groningen, the hunt escape groningen, the hunt escaperoom groningen</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>The Hunt Groningen</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Outdoor Escape in Groningen</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Groningen</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Groningen</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Groningen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -760,110 +790,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>The Hunt Winschoten</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-winschoten/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>the hunt winschoten, escape game the hunt winschoten, the hunt escape winschoten, the hunt escaperoom winschoten</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>The Hunt Winschoten</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Outdoor Escape in Winschoten</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Winschoten</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Winschoten</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Winschoten. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -872,110 +912,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>The Hunt Leeuwarden</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-leeuwarden/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>the hunt leeuwarden, escape game the hunt leeuwarden, the hunt escape leeuwarden, the hunt escaperoom leeuwarden</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>The Hunt Leeuwarden</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Outdoor Escape in Leeuwarden</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Leeuwarden</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Leeuwarden</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Leeuwarden. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -984,110 +1034,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>The Hunt Drachten</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-drachten/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>the hunt drachten, escape game the hunt drachten, the hunt escape drachten, the hunt escaperoom drachten</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>The Hunt Drachten</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Outdoor Escape in Drachten</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Drachten</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Drachten</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Drachten. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1096,110 +1156,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>The Hunt Heerenveen</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-heerenveen/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>the hunt heerenveen, escape game the hunt heerenveen, the hunt escape heerenveen, the hunt escaperoom heerenveen</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>The Hunt Heerenveen</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Outdoor Escape in Heerenveen</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Heerenveen</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Heerenveen</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Heerenveen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1208,110 +1278,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>The Hunt Assen</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-assen/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>the hunt assen, escape game the hunt assen, the hunt escape assen, the hunt escaperoom assen</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>The Hunt Assen</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Outdoor Escape in Assen</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Assen</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Assen</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Assen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1320,110 +1400,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>The Hunt Emmen</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-emmen/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>the hunt emmen, escape game the hunt emmen, the hunt escape emmen, the hunt escaperoom emmen</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>The Hunt Emmen</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Outdoor Escape in Emmen</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Emmen</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Emmen</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Emmen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1432,110 +1522,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>The Hunt Meppel</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-meppel/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>the hunt meppel, escape game the hunt meppel, the hunt escape meppel, the hunt escaperoom meppel</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>The Hunt Meppel</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Outdoor Escape in Meppel</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Meppel</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Meppel</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Meppel. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1544,110 +1644,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>The Hunt Zwolle</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-zwolle/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>the hunt zwolle, escape game the hunt zwolle, the hunt escape zwolle, the hunt escaperoom zwolle</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>The Hunt Zwolle</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Outdoor Escape in Zwolle</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Zwolle</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Zwolle</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Zwolle. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1656,110 +1766,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>The Hunt Kampen</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-kampen/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>the hunt kampen, escape game the hunt kampen, the hunt escape kampen, the hunt escaperoom kampen</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>The Hunt Kampen</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Outdoor Escape in Kampen</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Kampen</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Kampen</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Kampen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1768,110 +1888,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>The Hunt Steenwijk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-steenwijk/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>the hunt steenwijk, escape game the hunt steenwijk, the hunt escape steenwijk, the hunt escaperoom steenwijk</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>The Hunt Steenwijk</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Outdoor Escape in Steenwijk</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Steenwijk</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Steenwijk</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Steenwijk. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1880,110 +2010,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>The Hunt Deventer</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-deventer/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>the hunt deventer, escape game the hunt deventer, the hunt escape deventer, the hunt escaperoom deventer</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>The Hunt Deventer</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Outdoor Escape in Deventer</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Deventer</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Deventer</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Deventer. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -1992,110 +2132,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>The Hunt Almelo</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-almelo/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>the hunt almelo, escape game the hunt almelo, the hunt escape almelo, the hunt escaperoom almelo</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>The Hunt Almelo</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Outdoor Escape in Almelo</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Almelo</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Almelo</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Almelo. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2104,110 +2254,120 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>The Hunt Enschede</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-enschede/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>the hunt enschede, escape game the hunt enschede, the hunt escape enschede, the hunt escaperoom enschede</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>The Hunt Enschede</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Outdoor Escape in Enschede</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Enschede</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Enschede</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Enschede. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2216,110 +2376,120 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>The Hunt Oldenzaal</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-oldenzaal/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>the hunt oldenzaal, escape game the hunt oldenzaal, the hunt escape oldenzaal, the hunt escaperoom oldenzaal</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>The Hunt Oldenzaal</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Outdoor Escape in Oldenzaal</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Oldenzaal</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Oldenzaal</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Oldenzaal. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2328,110 +2498,120 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>The Hunt Almere</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-almere/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>the hunt almere, escape game the hunt almere, the hunt escape almere, the hunt escaperoom almere</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>The Hunt Almere</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Outdoor Escape in Almere</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Almere</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Almere</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Almere. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2440,110 +2620,120 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>The Hunt Arnhem</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-arnhem/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>the hunt arnhem, escape game the hunt arnhem, the hunt escape arnhem, the hunt escaperoom arnhem</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>The Hunt Arnhem</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Outdoor Escape in Arnhem</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Arnhem</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Arnhem</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Arnhem. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2552,110 +2742,120 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>The Hunt Nijmegen</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-nijmegen/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>the hunt nijmegen, escape game the hunt nijmegen, the hunt escape nijmegen, the hunt escaperoom nijmegen</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>The Hunt Nijmegen</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Outdoor Escape in Nijmegen</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Nijmegen</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Nijmegen</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Nijmegen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2664,110 +2864,120 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>The Hunt Utrecht</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-utrecht/</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>the hunt utrecht, escape game the hunt utrecht, the hunt escape utrecht, the hunt escaperoom utrecht</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>The Hunt Utrecht</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Outdoor Escape in Utrecht</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Utrecht</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Utrecht</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Utrecht. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2776,110 +2986,120 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>The Hunt Amersfoort</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-amersfoort/</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>the hunt amersfoort, escape game the hunt amersfoort, the hunt escape amersfoort, the hunt escaperoom amersfoort</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>The Hunt Amersfoort</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Outdoor Escape in Amersfoort</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Amersfoort</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Amersfoort</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Amersfoort. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -2888,110 +3108,120 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>The Hunt Amsterdam</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-amsterdam/</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>the hunt amsterdam, escape game the hunt amsterdam, the hunt escape amsterdam, the hunt escaperoom amsterdam</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>The Hunt Amsterdam</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Outdoor Escape in Amsterdam</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Amsterdam</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Amsterdam</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Amsterdam. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3000,110 +3230,120 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>The Hunt Haarlem</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-haarlem/</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>the hunt haarlem, escape game the hunt haarlem, the hunt escape haarlem, the hunt escaperoom haarlem</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>The Hunt Haarlem</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Outdoor Escape in Haarlem</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Haarlem</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Haarlem</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Haarlem. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3112,110 +3352,120 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>The Hunt Alkmaar</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-alkmaar/</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>the hunt alkmaar, escape game the hunt alkmaar, the hunt escape alkmaar, the hunt escaperoom alkmaar</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>The Hunt Alkmaar</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Outdoor Escape in Alkmaar</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Alkmaar</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Alkmaar</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Alkmaar. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3224,110 +3474,120 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>The Hunt Rotterdam</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-rotterdam-2/</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>the hunt rotterdam, escape game the hunt rotterdam, the hunt escape rotterdam, the hunt escaperoom rotterdam</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>The Hunt Rotterdam</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Outdoor Escape in Rotterdam</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Rotterdam</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Rotterdam</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Rotterdam. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3336,110 +3596,120 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>The Hunt Den Haag</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-den-haag/</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>the hunt den haag, escape game the hunt den haag, the hunt escape den haag, the hunt escaperoom den haag</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>The Hunt Den Haag</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Outdoor Escape in Den Haag</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Den Haag</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Den Haag</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Den Haag. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3448,110 +3718,120 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>The Hunt Zoetermeer</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-zoetermeer/</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>the hunt zoetermeer, escape game the hunt zoetermeer, the hunt escape zoetermeer, the hunt escaperoom zoetermeer</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>The Hunt Zoetermeer</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Outdoor Escape in Zoetermeer</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Zoetermeer</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Zoetermeer</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Zoetermeer. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3560,110 +3840,120 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>The Hunt Dordrecht</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-dordrecht/</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>the hunt dordrecht, escape game the hunt dordrecht, the hunt escape dordrecht, the hunt escaperoom dordrecht</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>The Hunt Dordrecht</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Outdoor Escape in Dordrecht</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Dordrecht</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Dordrecht</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Dordrecht. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3672,110 +3962,120 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>The Hunt Middelburg</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-middelburg/</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>the hunt middelburg, escape game the hunt middelburg, the hunt escape middelburg, the hunt escaperoom middelburg</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>The Hunt Middelburg</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Outdoor Escape in Middelburg</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Middelburg</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Middelburg</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Middelburg. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3784,110 +4084,120 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>The Hunt Terneuzen</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-terneuzen/</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>the hunt terneuzen, escape game the hunt terneuzen, the hunt escape terneuzen, the hunt escaperoom terneuzen</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>The Hunt Terneuzen</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Outdoor Escape in Terneuzen</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Terneuzen</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Terneuzen</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Terneuzen. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -3896,110 +4206,120 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>The Hunt Eindhoven</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-eindhoven/</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>the hunt eindhoven, escape game the hunt eindhoven, the hunt escape eindhoven, the hunt escaperoom eindhoven</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>The Hunt Eindhoven</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Outdoor Escape in Eindhoven</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Eindhoven</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Eindhoven</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Eindhoven. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -4008,110 +4328,120 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>The Hunt Tilburg</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-tilburg/</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>the hunt tilburg, escape game the hunt tilburg, the hunt escape tilburg, the hunt escaperoom tilburg</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>The Hunt Tilburg</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Outdoor Escape in Tilburg</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Tilburg</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Tilburg</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Tilburg. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -4120,110 +4450,120 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>The Hunt Maastricht</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-maastricht/</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>the hunt maastricht, escape game the hunt maastricht, the hunt escape maastricht, the hunt escaperoom maastricht</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>The Hunt Maastricht</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Outdoor Escape in Maastricht</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Maastricht</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Maastricht</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Maastricht. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -4232,110 +4572,4268 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>The Hunt - Merk</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>The Hunt Venlo</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-venlo/</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>the hunt venlo, escape game the hunt venlo, the hunt escape venlo, the hunt escaperoom venlo</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>The Hunt Venlo</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Escape Game The Hunt</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Ontsnap aan Live Hunters</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Echte Hunters Jagen op Jullie</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Outdoor Escape in Venlo</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>90 Minuten Pure Spanning</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Live Hunters op Jullie Hielen</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Teamuitje met Live Hunters</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Vrijgezellenfeest Venlo</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Bedrijfsuitje Venlo</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Officiële Site The Hunt</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Vanaf 8 tot 200 Personen</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Puzzelen, Rennen, Ontsnappen</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>Vrijblijvend Aanvragen</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>De Stad Is Jullie Speelveld</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Ontsnap 90 minuten aan echte live Hunters in Venlo. Puzzelen, rennen en samenwerken!</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hunted spelen - Algemeen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>hunted spel, hunted spelen, zelf hunted spelen, hunted spel spelen, hunted uitje, hunted teamuitje, hunted bedrijfsuitje, hunted vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Outdoor Escape Game</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest The Hunt</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in jouw stad. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hunted Groningen</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-groningen/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>hunted groningen, hunted spel groningen, hunted spelen groningen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Groningen</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Groningen</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Groningen</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Groningen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hunted Winschoten</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-winschoten/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>hunted winschoten, hunted spel winschoten, hunted spelen winschoten</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Winschoten</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Winschoten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Winschoten</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Winschoten. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hunted Leeuwarden</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-leeuwarden/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>hunted leeuwarden, hunted spel leeuwarden, hunted spelen leeuwarden</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Leeuwarden</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Leeuwarden</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Leeuwarden</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Leeuwarden. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hunted Drachten</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-drachten/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>hunted drachten, hunted spel drachten, hunted spelen drachten</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Drachten</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Drachten</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Drachten</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Drachten. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hunted Heerenveen</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-heerenveen/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>hunted heerenveen, hunted spel heerenveen, hunted spelen heerenveen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Heerenveen</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Heerenveen</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Heerenveen</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Heerenveen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hunted Assen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-assen/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>hunted assen, hunted spel assen, hunted spelen assen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Assen</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Assen</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Assen</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Assen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hunted Emmen</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-emmen/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>hunted emmen, hunted spel emmen, hunted spelen emmen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Emmen</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Emmen</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Emmen</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Emmen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hunted Meppel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-meppel/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>hunted meppel, hunted spel meppel, hunted spelen meppel</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Meppel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Meppel</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Meppel</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Meppel. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hunted Zwolle</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-zwolle/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>hunted zwolle, hunted spel zwolle, hunted spelen zwolle</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Zwolle</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Zwolle</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Zwolle</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Zwolle. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Hunted Kampen</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-kampen/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>hunted kampen, hunted spel kampen, hunted spelen kampen</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Kampen</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Kampen</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Kampen</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Kampen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hunted Steenwijk</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-steenwijk/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>hunted steenwijk, hunted spel steenwijk, hunted spelen steenwijk</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Steenwijk</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Steenwijk</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Steenwijk</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Steenwijk. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hunted Deventer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-deventer/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>hunted deventer, hunted spel deventer, hunted spelen deventer</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Deventer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Deventer</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Deventer</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Deventer. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hunted Almelo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-almelo/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>hunted almelo, hunted spel almelo, hunted spelen almelo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Almelo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Almelo</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Almelo</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Almelo. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hunted Enschede</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-enschede/</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>hunted enschede, hunted spel enschede, hunted spelen enschede</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Enschede</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Enschede</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Enschede</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Enschede. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Hunted Oldenzaal</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-oldenzaal/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>hunted oldenzaal, hunted spel oldenzaal, hunted spelen oldenzaal</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Oldenzaal</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Oldenzaal</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Oldenzaal</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Oldenzaal. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hunted Almere</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-almere/</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>hunted almere, hunted spel almere, hunted spelen almere</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Almere</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Almere</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Almere</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Almere. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hunted Arnhem</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-arnhem/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>hunted arnhem, hunted spel arnhem, hunted spelen arnhem</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Arnhem</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Arnhem</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Arnhem</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Arnhem. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hunted Nijmegen</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-nijmegen/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>hunted nijmegen, hunted spel nijmegen, hunted spelen nijmegen</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Nijmegen</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Nijmegen</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Nijmegen</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Nijmegen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hunted Utrecht</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-utrecht/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>hunted utrecht, hunted spel utrecht, hunted spelen utrecht</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Utrecht</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Utrecht</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Utrecht</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Utrecht. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hunted Amersfoort</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-amersfoort/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>hunted amersfoort, hunted spel amersfoort, hunted spelen amersfoort</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Amersfoort</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Amersfoort</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Amersfoort</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Amersfoort. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Hunted Amsterdam</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-amsterdam/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>hunted amsterdam, hunted spel amsterdam, hunted spelen amsterdam</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Amsterdam</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Amsterdam</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Amsterdam</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Amsterdam. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hunted Haarlem</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-haarlem/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>hunted haarlem, hunted spel haarlem, hunted spelen haarlem</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Haarlem</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Haarlem</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Haarlem</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Haarlem. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hunted Alkmaar</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-alkmaar/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>hunted alkmaar, hunted spel alkmaar, hunted spelen alkmaar</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Alkmaar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Alkmaar</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Alkmaar</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Alkmaar. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hunted Rotterdam</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-rotterdam-2/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>hunted rotterdam, hunted spel rotterdam, hunted spelen rotterdam</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Rotterdam</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Rotterdam</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Rotterdam</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Rotterdam. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hunted Den Haag</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-den-haag/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>hunted den haag, hunted spel den haag, hunted spelen den haag</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Den Haag</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Den Haag</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Den Haag</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Den Haag. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hunted Zoetermeer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-zoetermeer/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>hunted zoetermeer, hunted spel zoetermeer, hunted spelen zoetermeer</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Zoetermeer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Zoetermeer</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Zoetermeer</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Zoetermeer. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hunted Dordrecht</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-dordrecht/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>hunted dordrecht, hunted spel dordrecht, hunted spelen dordrecht</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Dordrecht</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Dordrecht</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Dordrecht</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Dordrecht. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hunted Middelburg</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-middelburg/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>hunted middelburg, hunted spel middelburg, hunted spelen middelburg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Middelburg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Middelburg</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Middelburg</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Middelburg. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hunted Terneuzen</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-terneuzen/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>hunted terneuzen, hunted spel terneuzen, hunted spelen terneuzen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Terneuzen</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Terneuzen</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Terneuzen</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Terneuzen. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hunted Eindhoven</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-eindhoven/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>hunted eindhoven, hunted spel eindhoven, hunted spelen eindhoven</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Eindhoven</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Eindhoven</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Eindhoven</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Eindhoven. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hunted Tilburg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-tilburg/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>hunted tilburg, hunted spel tilburg, hunted spelen tilburg</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Tilburg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Tilburg</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Tilburg</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Tilburg. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hunted Maastricht</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-maastricht/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>hunted maastricht, hunted spel maastricht, hunted spelen maastricht</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Maastricht</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Maastricht</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Maastricht</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Maastricht. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>The Hunt - Hunted</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hunted Venlo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/escape-game-the-hunt-locaties/escape-game-the-hunt-venlo/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>hunted venlo, hunted spel venlo, hunted spelen venlo</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Zelf Opgejaagd in Venlo</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Speel Het Zelf: The Hunt</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>90 Minuten Opgejaagd Worden</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Venlo</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Venlo</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vanaf 8 tot 200 Personen</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Blijf Uit Handen van Hunters</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ontsnap 90 minuten aan echte live Hunters in Venlo. Puzzelen, rennen en samenwerken!</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ideaal als teamuitje, bedrijfsuitje of vrijgezellenfeest. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
         </is>
@@ -4352,7 +8850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4363,79 +8861,79 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>The Hunt - Merk</t>
+          <t>Dagbudget (€)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Standaard max. bod (€)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Afwijkende biedingen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Uitsluitingen (woordgroep)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>The Hunt - Merk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zoeken (alleen Google Zoeken, geen partners/display)</t>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Amersfoort € 1.00, Zwolle € 0.90</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>film, movie, netflix, trailer, imdb, cast, showdown, ps4, ps5, xbox, steam, download, torrent, escape hunt, vacature, werken bij, serie, boek</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>The Hunt - Hunted</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gepauzeerd (eerst nakijken)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dagbudget</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>€ 5.00</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>film, movie, netflix, trailer, imdb, cast, showdown, ps4, ps5, xbox, steam, download, torrent, escape hunt, vacature, werken bij, serie, boek, kijken, npo, videoland, seizoen, aflevering, deelnemers, aanmelden, meedoen, uitzending, avrotros, kijkcijfers, vip</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bieden</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Handmatige CPC, max € 0.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Taal / locatie</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nederlands / Nederland</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Uitsluitingen (woordgroep)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>film, movie, netflix, trailer, imdb, cast, showdown, ps4, ps5, xbox, steam, download, torrent, escape hunt, vacature, werken bij, serie, boek</t>
+          <t>Alle campagnes: alleen Google Zoeken (geen partners/display), Nederlands, heel Nederland, handmatige CPC, status Gepauzeerd.</t>
         </is>
       </c>
     </row>

--- a/tools/seo/ads/merkcampagne/merkcampagne-overzicht.xlsx
+++ b/tools/seo/ads/merkcampagne/merkcampagne-overzicht.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8836,6 +8836,1592 @@
       <c r="X69" t="inlineStr">
         <is>
           <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie groep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Utrecht</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-utrecht/</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest utrecht, vrijgezellenuitje utrecht, vrijgezellendag utrecht</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Utrecht</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Utrecht</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Utrecht: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Rotterdam</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-rotterdam-perfect-groepen/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest rotterdam, vrijgezellenuitje rotterdam, vrijgezellendag rotterdam</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Rotterdam</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Rotterdam</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Rotterdam: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Amsterdam</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-amsterdam/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest amsterdam, vrijgezellenuitje amsterdam, vrijgezellendag amsterdam</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Amsterdam</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Amsterdam</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Amsterdam: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Groningen</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-groningen-het-meest-actieve-avontuur-voor-de-bruidegom/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest groningen, vrijgezellenuitje groningen, vrijgezellendag groningen</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Groningen</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Groningen</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Groningen: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Amersfoort</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-amersfoort-wie-van-jullie-weet-te-ontsnappen-aan-de-hunters/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest amersfoort, vrijgezellenuitje amersfoort, vrijgezellendag amersfoort</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Amersfoort</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Amersfoort</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Amersfoort: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Zwolle</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-zwolle/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest zwolle, vrijgezellenuitje zwolle, vrijgezellendag zwolle</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Zwolle</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Zwolle</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Zwolle: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Nijmegen</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-nijmegen-beleef-een-onvergetelijk-avontuur-met-escape-game-the-hunt/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest nijmegen, vrijgezellenuitje nijmegen, vrijgezellendag nijmegen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Nijmegen</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Nijmegen</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Nijmegen: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Maastricht</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/vrijgezellenfeest-maastricht/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest maastricht, vrijgezellenuitje maastricht, vrijgezellendag maastricht</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest Maastricht</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Actief Vrijgezellenuitje</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Maastricht</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Wie Ontsnapt aan de Hunters?</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Vanaf 8 Personen</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Ontsnappen</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Aanvragen</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Origineel Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Voor Bruid én Bruidegom</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Vrijgezellenfeest in Maastricht: ontsnap 90 minuten aan echte live Hunters in de stad.</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en samenwerken. Een actief uitje voor groepen vanaf 8 personen.</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum aan voor jullie feest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>The Hunt - Teamuitje</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Groningen</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/bedrijfsuitje-groningen-combineer-stad/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje groningen</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Groningen</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Teamuitje Groningen</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Teambuilding in de Buitenlucht</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Van 8 tot 200 Collega's</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Samenwerken</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Groningen</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Offerte Aanvragen</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Ook Op Maat Mogelijk</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje in Groningen: ontsnap 90 minuten met je collega's aan echte live Hunters.</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en strategie: teambuilding die energie geeft. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum en offerte aan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>The Hunt - Teamuitje</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Teamuitje Zwolle</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/teamuitje-bedrijfsuitje-zwolle/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>teamuitje zwolle</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Teamuitje Zwolle</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Zwolle</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Teambuilding in de Buitenlucht</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Van 8 tot 200 Collega's</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Samenwerken</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Zwolle</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Offerte Aanvragen</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Ook Op Maat Mogelijk</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Teamuitje in Zwolle: ontsnap 90 minuten met je collega's aan echte live Hunters.</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en strategie: teambuilding die energie geeft. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum en offerte aan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>The Hunt - Teamuitje</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Teamuitje Tilburg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/teamuitje-tilburg-organiseren-beleef-90-minuten-actie-met-the-hunt/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>teamuitje tilburg</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Teamuitje Tilburg</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Tilburg</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Teambuilding in de Buitenlucht</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Van 8 tot 200 Collega's</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Samenwerken</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Tilburg</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Offerte Aanvragen</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Ook Op Maat Mogelijk</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Teamuitje in Tilburg: ontsnap 90 minuten met je collega's aan echte live Hunters.</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en strategie: teambuilding die energie geeft. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum en offerte aan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>The Hunt - Teamuitje</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Enschede</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/teamuitje-bedrijfsuitje-enschede/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje enschede</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Enschede</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Teamuitje Enschede</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Teambuilding in de Buitenlucht</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Van 8 tot 200 Collega's</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Samenwerken</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Enschede</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Offerte Aanvragen</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Ook Op Maat Mogelijk</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje in Enschede: ontsnap 90 minuten met je collega's aan echte live Hunters.</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en strategie: teambuilding die energie geeft. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum en offerte aan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>The Hunt - Teamuitje</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Teamuitje + Bedrijfsuitje Leeuwarden</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://escapegamethehunt.nl/teamuitje-bedrijfsuitje-leeuwarden/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>teamuitje leeuwarden, bedrijfsuitje leeuwarden</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Teamuitje Leeuwarden</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ontsnap aan Live Hunters</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Echte Hunters Jagen op Jullie</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Teamuitje met Live Hunters</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Bedrijfsuitje Leeuwarden</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Teambuilding in de Buitenlucht</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>90 Minuten Pure Spanning</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Escape Game The Hunt</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Van 8 tot 200 Collega's</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Puzzelen, Rennen, Samenwerken</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Outdoor Escape in Leeuwarden</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Live Hunters op Jullie Hielen</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Vrijblijvend Offerte Aanvragen</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>De Stad Is Jullie Speelveld</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Ook Op Maat Mogelijk</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Teamuitje in Leeuwarden: ontsnap 90 minuten met je collega's aan echte live Hunters.</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Geen kamer maar de hele stad als speelveld. Live Hunters zitten jullie op de hielen.</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Puzzelen, rennen en strategie: teambuilding die energie geeft. Van 8 tot 200 personen.</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Dé escape game met live Hunters. Vraag vrijblijvend een datum en offerte aan.</t>
         </is>
       </c>
     </row>
@@ -8850,7 +10436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8930,8 +10516,54 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The Hunt - Vrijgezellenfeest</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vacature, werken bij, escape hunt, gratis, kinderfeestje, kinderen</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>The Hunt - Teamuitje</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vacature, werken bij, escape hunt, gratis, kinderfeestje, kinderen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Alle campagnes: alleen Google Zoeken (geen partners/display), Nederlands, heel Nederland, handmatige CPC, status Gepauzeerd.</t>
         </is>
